--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123652963</v>
       </c>
       <c r="B2" t="n">
-        <v>58341</v>
+        <v>58347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123652963</v>
       </c>
       <c r="B2" t="n">
-        <v>58347</v>
+        <v>58350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123652963</v>
       </c>
       <c r="B2" t="n">
-        <v>58350</v>
+        <v>58351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98425</v>
+        <v>98811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98811</v>
+        <v>98898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98898</v>
+        <v>98901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98901</v>
+        <v>98927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98927</v>
+        <v>98928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98928</v>
+        <v>98929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98929</v>
+        <v>98931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>126759989</v>
       </c>
       <c r="B3" t="n">
-        <v>98931</v>
+        <v>98935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,132 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132440835</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58810</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lugnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>702421</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6649945</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>132440835</v>
       </c>
       <c r="B4" t="n">
-        <v>58810</v>
+        <v>58811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>132440835</v>
       </c>
       <c r="B4" t="n">
-        <v>58811</v>
+        <v>58815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>132440835</v>
       </c>
       <c r="B4" t="n">
-        <v>58815</v>
+        <v>58816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>132440835</v>
       </c>
       <c r="B4" t="n">
-        <v>58816</v>
+        <v>58819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>132440835</v>
       </c>
       <c r="B4" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123652963</v>
+        <v>123608827</v>
       </c>
       <c r="B2" t="n">
-        <v>58373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,25 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -718,27 +716,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnet, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702421</v>
+        <v>702535</v>
       </c>
       <c r="R2" t="n">
-        <v>6649945</v>
+        <v>6649870</v>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,31 +756,35 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Jagad av korpar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,62 +803,68 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126759989</v>
+        <v>84321801</v>
       </c>
       <c r="B3" t="n">
-        <v>98935</v>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ytternäsvägen 68, Upl</t>
+          <t>Ytternäsvägen 68,Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702525</v>
+        <v>702549</v>
       </c>
       <c r="R3" t="n">
-        <v>6649944</v>
+        <v>6649894</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +888,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2020-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2020-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132440835</v>
+        <v>84998950</v>
       </c>
       <c r="B4" t="n">
-        <v>58820</v>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,56 +941,57 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äggläggande</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Upl</t>
+          <t>Ytternäsvägen 68,Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702421</v>
+        <v>702549</v>
       </c>
       <c r="R4" t="n">
-        <v>6649945</v>
+        <v>6649894</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,22 +1015,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,6 +1054,634 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>84321821</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ytternäsvägen 68,Norrtälje, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>702549</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6649894</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123652963</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lugnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>702421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6649945</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115953237</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lugnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>702260</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6650001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50-60 som spelade och la rom.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132440835</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lugnet, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>702421</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6649945</v>
+      </c>
+      <c r="S8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126759989</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ytternäsvägen 68, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>702525</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6649944</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22190-2024 artfynd.xlsx
+++ b/artfynd/A 22190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123608827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84321801</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1069,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84998950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1181,6 +1201,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84321821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1306,6 +1331,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652963</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1435,6 +1465,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115953237</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132440835</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1682,8 +1722,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126759989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>